--- a/信息检索与数据挖掘作业/第三次论文研读/数据备份.xlsx
+++ b/信息检索与数据挖掘作业/第三次论文研读/数据备份.xlsx
@@ -76,10 +76,10 @@
     <t>Ambiguous Instance-Aware Contrastive Network with Multi-Level Matching for Multi-View Document Clustering | Proceedings of the AAAI Conference on Artificial Intelligence</t>
   </si>
   <si>
+    <t>https://www.doubao.com/thread/w838ad428c17559ec</t>
+  </si>
+  <si>
     <t>https://jcn5ed29kssw.feishu.cn/wiki/WIv9wIeE9ig0e0kBSg9cTpYqnGb?from=from_copylink</t>
-  </si>
-  <si>
-    <t>https://www.doubao.com/thread/w838ad428c17559ec</t>
   </si>
   <si>
     <t>作者聚焦多视图文档聚类（MvDC）任务，旨在解决现有方法的两大核心痛点：一是多视图数据对齐视角单一，多数方法仅从特征或类别等单维度对齐，忽略数据表示的多样性与全面性，难以充分挖掘多视图互补性；二是对比学习中实例处理同质化，未区分易分类的 “清晰实例” 与难分类的 “模糊实例”，削弱模型判别能力，尤其在多语言文档等复杂场景中，这些问题导致聚类准确性与鲁棒性不足。</t>
@@ -729,7 +729,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -741,9 +741,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1116,10 +1113,10 @@
       <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="3" t="s">
